--- a/outbreaks/data/dx_readiness_comp_data_wo_COVID_20250212.xlsx
+++ b/outbreaks/data/dx_readiness_comp_data_wo_COVID_20250212.xlsx
@@ -1054,7 +1054,7 @@
         <v>28</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1140,7 +1140,7 @@
         <v>111</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
